--- a/diseases/d039/1995-1999.xlsx
+++ b/diseases/d039/1995-1999.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -22003,7 +22003,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -24365,7 +24365,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -25546,7 +25546,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -31451,7 +31451,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -34994,7 +34994,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41528,7 +41528,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42709,7 +42709,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43890,7 +43890,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -45071,7 +45071,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -46252,7 +46252,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -48614,7 +48614,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49795,7 +49795,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -51605,7 +51605,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -52786,7 +52786,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -53967,7 +53967,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -55148,7 +55148,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -56329,7 +56329,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -57510,7 +57510,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -58691,7 +58691,7 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN294" t="b">
@@ -59872,7 +59872,7 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN300" t="b">
@@ -61053,7 +61053,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -62234,7 +62234,7 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN312" t="b">
@@ -63415,7 +63415,7 @@
       </c>
       <c r="AM318" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN318" t="b">
@@ -64596,7 +64596,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN324" t="b">

--- a/diseases/d039/1995-1999.xlsx
+++ b/diseases/d039/1995-1999.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21143,6 +21143,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22003,7 +22008,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22563,6 +22568,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23184,7 +23194,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23744,6 +23754,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24365,7 +24380,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24925,6 +24940,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25546,7 +25566,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -26106,6 +26126,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26727,7 +26752,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27287,6 +27312,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27908,7 +27938,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -28468,6 +28498,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29089,7 +29124,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -29649,6 +29684,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30270,7 +30310,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -30830,6 +30870,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31451,7 +31496,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -32011,6 +32056,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32632,7 +32682,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -33192,6 +33242,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33813,7 +33868,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -34373,6 +34428,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34994,7 +35054,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -35944,6 +36004,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36804,7 +36869,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37364,6 +37429,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37985,7 +38055,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38545,6 +38615,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39166,7 +39241,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39726,6 +39801,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40347,7 +40427,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40907,6 +40987,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41528,7 +41613,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42088,6 +42173,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42709,7 +42799,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43269,6 +43359,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43890,7 +43985,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44450,6 +44545,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45071,7 +45171,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45631,6 +45731,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46252,7 +46357,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46812,6 +46917,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47433,7 +47543,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47993,6 +48103,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48614,7 +48729,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49174,6 +49289,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49795,7 +49915,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -50745,6 +50865,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51605,7 +51730,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -52165,6 +52290,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52786,7 +52916,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -53346,6 +53476,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53967,7 +54102,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -54527,6 +54662,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55148,7 +55288,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -55708,6 +55848,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56329,7 +56474,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -56889,6 +57034,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57510,7 +57660,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -58070,6 +58220,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58691,7 +58846,7 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN294" t="b">
@@ -59251,6 +59406,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59872,7 +60032,7 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN300" t="b">
@@ -60432,6 +60592,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61053,7 +61218,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -61613,6 +61778,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62234,7 +62404,7 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN312" t="b">
@@ -62794,6 +62964,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63415,7 +63590,7 @@
       </c>
       <c r="AM318" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN318" t="b">
@@ -63975,6 +64150,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64596,7 +64776,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN324" t="b">

--- a/diseases/d039/1995-1999.xlsx
+++ b/diseases/d039/1995-1999.xlsx
@@ -21138,6 +21138,11 @@
       <c r="Q104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21150,13 +21155,23 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
       </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV104" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22548,6 +22563,11 @@
       <c r="Q111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22560,13 +22580,23 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
       </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV111" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23719,6 +23749,11 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23731,13 +23766,23 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24890,6 +24935,11 @@
       <c r="Q123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24902,13 +24952,23 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
       </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV123" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26061,6 +26121,11 @@
       <c r="Q129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26073,13 +26138,23 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
       </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV129" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27232,6 +27307,11 @@
       <c r="Q135" t="n">
         <v>0</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27244,13 +27324,23 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
       </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV135" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28403,6 +28493,11 @@
       <c r="Q141" t="n">
         <v>0</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28415,13 +28510,23 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
       </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV141" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29574,6 +29679,11 @@
       <c r="Q147" t="n">
         <v>0</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29586,13 +29696,23 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
       </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV147" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30745,6 +30865,11 @@
       <c r="Q153" t="n">
         <v>0</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30757,13 +30882,23 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
       </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV153" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31916,6 +32051,11 @@
       <c r="Q159" t="n">
         <v>0</v>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31928,13 +32068,23 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
       </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV159" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33087,6 +33237,11 @@
       <c r="Q165" t="n">
         <v>0</v>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33099,13 +33254,23 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
       </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV165" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34258,6 +34423,11 @@
       <c r="Q171" t="n">
         <v>0</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34270,13 +34440,23 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
       </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV171" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -35819,6 +35999,11 @@
       <c r="Q179" t="n">
         <v>0</v>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35831,13 +36016,23 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
       </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV179" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37229,6 +37424,11 @@
       <c r="Q186" t="n">
         <v>0</v>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37241,13 +37441,23 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
       </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV186" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38400,6 +38610,11 @@
       <c r="Q192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38412,13 +38627,23 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
       </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV192" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39571,6 +39796,11 @@
       <c r="Q198" t="n">
         <v>0</v>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39583,13 +39813,23 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
       </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV198" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -40742,6 +40982,11 @@
       <c r="Q204" t="n">
         <v>0</v>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40754,13 +40999,23 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
       </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV204" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41913,6 +42168,11 @@
       <c r="Q210" t="n">
         <v>0</v>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41925,13 +42185,23 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
       </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV210" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43084,6 +43354,11 @@
       <c r="Q216" t="n">
         <v>0</v>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43096,13 +43371,23 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
       </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV216" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -44255,6 +44540,11 @@
       <c r="Q222" t="n">
         <v>0</v>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44267,13 +44557,23 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
       </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV222" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -45426,6 +45726,11 @@
       <c r="Q228" t="n">
         <v>0</v>
       </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45438,13 +45743,23 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
         <v>0</v>
       </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV228" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -46597,6 +46912,11 @@
       <c r="Q234" t="n">
         <v>0</v>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46609,13 +46929,23 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
         <v>0</v>
       </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV234" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -47768,6 +48098,11 @@
       <c r="Q240" t="n">
         <v>0</v>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47780,13 +48115,23 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
         <v>0</v>
       </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV240" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48939,6 +49284,11 @@
       <c r="Q246" t="n">
         <v>0</v>
       </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48951,13 +49301,23 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
         <v>0</v>
       </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV246" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -50500,6 +50860,11 @@
       <c r="Q254" t="n">
         <v>0</v>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50512,13 +50877,23 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
         <v>0</v>
       </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV254" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -51910,6 +52285,11 @@
       <c r="Q261" t="n">
         <v>0</v>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51922,13 +52302,23 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
         <v>0</v>
       </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV261" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -53081,6 +53471,11 @@
       <c r="Q267" t="n">
         <v>0</v>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53093,13 +53488,23 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
         <v>0</v>
       </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV267" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -54252,6 +54657,11 @@
       <c r="Q273" t="n">
         <v>0</v>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54264,13 +54674,23 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
         <v>0</v>
       </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV273" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -55423,6 +55843,11 @@
       <c r="Q279" t="n">
         <v>0</v>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -55435,13 +55860,23 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr"/>
       <c r="AT279" t="n">
         <v>0</v>
       </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV279" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -56594,6 +57029,11 @@
       <c r="Q285" t="n">
         <v>0</v>
       </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -56606,13 +57046,23 @@
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS285" t="inlineStr"/>
       <c r="AT285" t="n">
         <v>0</v>
       </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV285" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -57765,6 +58215,11 @@
       <c r="Q291" t="n">
         <v>0</v>
       </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA291" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57777,13 +58232,23 @@
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS291" t="inlineStr"/>
       <c r="AT291" t="n">
         <v>0</v>
       </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV291" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -58936,6 +59401,11 @@
       <c r="Q297" t="n">
         <v>0</v>
       </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA297" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58948,13 +59418,23 @@
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR297" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS297" t="inlineStr"/>
       <c r="AT297" t="n">
         <v>0</v>
       </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV297" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -60107,6 +60587,11 @@
       <c r="Q303" t="n">
         <v>0</v>
       </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA303" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60119,13 +60604,23 @@
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR303" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS303" t="inlineStr"/>
       <c r="AT303" t="n">
         <v>0</v>
       </c>
+      <c r="AU303" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV303" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -61278,6 +61773,11 @@
       <c r="Q309" t="n">
         <v>0</v>
       </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61290,13 +61790,23 @@
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR309" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS309" t="inlineStr"/>
       <c r="AT309" t="n">
         <v>0</v>
       </c>
+      <c r="AU309" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV309" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -62449,6 +62959,11 @@
       <c r="Q315" t="n">
         <v>0</v>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA315" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62461,13 +62976,23 @@
       </c>
       <c r="AP315" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS315" t="inlineStr"/>
       <c r="AT315" t="n">
         <v>0</v>
       </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV315" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -63620,6 +64145,11 @@
       <c r="Q321" t="n">
         <v>0</v>
       </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63632,12 +64162,22 @@
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS321" t="inlineStr"/>
       <c r="AT321" t="n">
         <v>0</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV321" t="inlineStr">
         <is>
